--- a/backend/tests/fixtures/numericos.xlsx
+++ b/backend/tests/fixtures/numericos.xlsx
@@ -430,7 +430,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>7861234567898</v>
+        <v>5901234123457</v>
       </c>
     </row>
     <row r="4">
